--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696108</v>
+        <v>123696394</v>
       </c>
       <c r="B2" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556601</v>
+        <v>556497</v>
       </c>
       <c r="R2" t="n">
-        <v>6337896</v>
+        <v>6338027</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696205</v>
+        <v>123696505</v>
       </c>
       <c r="B3" t="n">
-        <v>100645</v>
+        <v>57640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556581</v>
+        <v>556541</v>
       </c>
       <c r="R3" t="n">
-        <v>6337916</v>
+        <v>6338033</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696732</v>
+        <v>123696205</v>
       </c>
       <c r="B4" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556592</v>
+        <v>556581</v>
       </c>
       <c r="R4" t="n">
-        <v>6338060</v>
+        <v>6337916</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696703</v>
+        <v>123696272</v>
       </c>
       <c r="B5" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,17 +1022,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556557</v>
+        <v>556538</v>
       </c>
       <c r="R5" t="n">
-        <v>6338080</v>
+        <v>6337910</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696925</v>
+        <v>123696108</v>
       </c>
       <c r="B6" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556652</v>
+        <v>556601</v>
       </c>
       <c r="R6" t="n">
-        <v>6338006</v>
+        <v>6337896</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696505</v>
+        <v>123696703</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>100662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,46 +1202,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556541</v>
+        <v>556557</v>
       </c>
       <c r="R7" t="n">
-        <v>6338033</v>
+        <v>6338080</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696272</v>
+        <v>123696925</v>
       </c>
       <c r="B8" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556538</v>
+        <v>556652</v>
       </c>
       <c r="R8" t="n">
-        <v>6337910</v>
+        <v>6338006</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696394</v>
+        <v>123696732</v>
       </c>
       <c r="B9" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556497</v>
+        <v>556592</v>
       </c>
       <c r="R9" t="n">
-        <v>6338027</v>
+        <v>6338060</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696394</v>
+        <v>123696505</v>
       </c>
       <c r="B2" t="n">
-        <v>100662</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556497</v>
+        <v>556541</v>
       </c>
       <c r="R2" t="n">
-        <v>6338027</v>
+        <v>6338033</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696505</v>
+        <v>123696272</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>100680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556541</v>
+        <v>556538</v>
       </c>
       <c r="R3" t="n">
-        <v>6338033</v>
+        <v>6337910</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696205</v>
+        <v>123696394</v>
       </c>
       <c r="B4" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556581</v>
+        <v>556497</v>
       </c>
       <c r="R4" t="n">
-        <v>6337916</v>
+        <v>6338027</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696272</v>
+        <v>123696205</v>
       </c>
       <c r="B5" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556538</v>
+        <v>556581</v>
       </c>
       <c r="R5" t="n">
-        <v>6337910</v>
+        <v>6337916</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696108</v>
+        <v>123696703</v>
       </c>
       <c r="B6" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556601</v>
+        <v>556557</v>
       </c>
       <c r="R6" t="n">
-        <v>6337896</v>
+        <v>6338080</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696703</v>
+        <v>123696925</v>
       </c>
       <c r="B7" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,14 +1226,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556557</v>
+        <v>556652</v>
       </c>
       <c r="R7" t="n">
-        <v>6338080</v>
+        <v>6338006</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696925</v>
+        <v>123696732</v>
       </c>
       <c r="B8" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,17 +1328,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556652</v>
+        <v>556592</v>
       </c>
       <c r="R8" t="n">
-        <v>6338006</v>
+        <v>6338060</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696732</v>
+        <v>123696108</v>
       </c>
       <c r="B9" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556592</v>
+        <v>556601</v>
       </c>
       <c r="R9" t="n">
-        <v>6338060</v>
+        <v>6337896</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696505</v>
+        <v>123696394</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>100682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556541</v>
+        <v>556497</v>
       </c>
       <c r="R2" t="n">
-        <v>6338033</v>
+        <v>6338027</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696272</v>
+        <v>123696108</v>
       </c>
       <c r="B3" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556538</v>
+        <v>556601</v>
       </c>
       <c r="R3" t="n">
-        <v>6337910</v>
+        <v>6337896</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696394</v>
+        <v>123696732</v>
       </c>
       <c r="B4" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556497</v>
+        <v>556592</v>
       </c>
       <c r="R4" t="n">
-        <v>6338027</v>
+        <v>6338060</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696205</v>
+        <v>123696505</v>
       </c>
       <c r="B5" t="n">
-        <v>100680</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,41 +993,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556581</v>
+        <v>556541</v>
       </c>
       <c r="R5" t="n">
-        <v>6337916</v>
+        <v>6338033</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>123696703</v>
       </c>
       <c r="B6" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696925</v>
+        <v>123696272</v>
       </c>
       <c r="B7" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556652</v>
+        <v>556538</v>
       </c>
       <c r="R7" t="n">
-        <v>6338006</v>
+        <v>6337910</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696732</v>
+        <v>123696205</v>
       </c>
       <c r="B8" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,17 +1328,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556592</v>
+        <v>556581</v>
       </c>
       <c r="R8" t="n">
-        <v>6338060</v>
+        <v>6337916</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696108</v>
+        <v>123696925</v>
       </c>
       <c r="B9" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556601</v>
+        <v>556652</v>
       </c>
       <c r="R9" t="n">
-        <v>6337896</v>
+        <v>6338006</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696394</v>
+        <v>123696732</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556497</v>
+        <v>556592</v>
       </c>
       <c r="R2" t="n">
-        <v>6338027</v>
+        <v>6338060</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696108</v>
+        <v>123696925</v>
       </c>
       <c r="B3" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556601</v>
+        <v>556652</v>
       </c>
       <c r="R3" t="n">
-        <v>6337896</v>
+        <v>6338006</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696732</v>
+        <v>123696205</v>
       </c>
       <c r="B4" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,17 +915,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556592</v>
+        <v>556581</v>
       </c>
       <c r="R4" t="n">
-        <v>6338060</v>
+        <v>6337916</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696703</v>
+        <v>123696272</v>
       </c>
       <c r="B6" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,17 +1124,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556557</v>
+        <v>556538</v>
       </c>
       <c r="R6" t="n">
-        <v>6338080</v>
+        <v>6337910</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696272</v>
+        <v>123696108</v>
       </c>
       <c r="B7" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,13 +1230,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556538</v>
+        <v>556601</v>
       </c>
       <c r="R7" t="n">
-        <v>6337910</v>
+        <v>6337896</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696205</v>
+        <v>123696703</v>
       </c>
       <c r="B8" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,14 +1328,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556581</v>
+        <v>556557</v>
       </c>
       <c r="R8" t="n">
-        <v>6337916</v>
+        <v>6338080</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696925</v>
+        <v>123696394</v>
       </c>
       <c r="B9" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556652</v>
+        <v>556497</v>
       </c>
       <c r="R9" t="n">
-        <v>6338006</v>
+        <v>6338027</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696732</v>
+        <v>123696925</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556592</v>
+        <v>556652</v>
       </c>
       <c r="R2" t="n">
-        <v>6338060</v>
+        <v>6338006</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696925</v>
+        <v>123696732</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556652</v>
+        <v>556592</v>
       </c>
       <c r="R3" t="n">
-        <v>6338006</v>
+        <v>6338060</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696925</v>
+        <v>123696272</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556652</v>
+        <v>556538</v>
       </c>
       <c r="R2" t="n">
-        <v>6338006</v>
+        <v>6337910</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696732</v>
+        <v>123696925</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556592</v>
+        <v>556652</v>
       </c>
       <c r="R3" t="n">
-        <v>6338060</v>
+        <v>6338006</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696205</v>
+        <v>123696505</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556581</v>
+        <v>556541</v>
       </c>
       <c r="R4" t="n">
-        <v>6337916</v>
+        <v>6338033</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696505</v>
+        <v>123696703</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,46 +998,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556541</v>
+        <v>556557</v>
       </c>
       <c r="R5" t="n">
-        <v>6338033</v>
+        <v>6338080</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696272</v>
+        <v>123696394</v>
       </c>
       <c r="B6" t="n">
         <v>100257</v>
@@ -1124,14 +1124,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556538</v>
+        <v>556497</v>
       </c>
       <c r="R6" t="n">
-        <v>6337910</v>
+        <v>6338027</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696703</v>
+        <v>123696732</v>
       </c>
       <c r="B8" t="n">
         <v>100257</v>
@@ -1332,13 +1332,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556557</v>
+        <v>556592</v>
       </c>
       <c r="R8" t="n">
-        <v>6338080</v>
+        <v>6338060</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696394</v>
+        <v>123696205</v>
       </c>
       <c r="B9" t="n">
         <v>100257</v>
@@ -1430,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556497</v>
+        <v>556581</v>
       </c>
       <c r="R9" t="n">
-        <v>6338027</v>
+        <v>6337916</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696272</v>
+        <v>123696394</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556538</v>
+        <v>556497</v>
       </c>
       <c r="R2" t="n">
-        <v>6337910</v>
+        <v>6338027</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696925</v>
+        <v>123696703</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -813,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556652</v>
+        <v>556557</v>
       </c>
       <c r="R3" t="n">
-        <v>6338006</v>
+        <v>6338080</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696505</v>
+        <v>123696272</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556541</v>
+        <v>556538</v>
       </c>
       <c r="R4" t="n">
-        <v>6338033</v>
+        <v>6337910</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696703</v>
+        <v>123696925</v>
       </c>
       <c r="B5" t="n">
         <v>100257</v>
@@ -1022,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556557</v>
+        <v>556652</v>
       </c>
       <c r="R5" t="n">
-        <v>6338080</v>
+        <v>6338006</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696394</v>
+        <v>123696505</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1095,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556497</v>
+        <v>556541</v>
       </c>
       <c r="R6" t="n">
-        <v>6338027</v>
+        <v>6338033</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696108</v>
+        <v>123696205</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556601</v>
+        <v>556581</v>
       </c>
       <c r="R7" t="n">
-        <v>6337896</v>
+        <v>6337916</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696732</v>
+        <v>123696108</v>
       </c>
       <c r="B8" t="n">
         <v>100257</v>
@@ -1328,17 +1328,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556592</v>
+        <v>556601</v>
       </c>
       <c r="R8" t="n">
-        <v>6338060</v>
+        <v>6337896</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696205</v>
+        <v>123696732</v>
       </c>
       <c r="B9" t="n">
         <v>100257</v>
@@ -1430,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556581</v>
+        <v>556592</v>
       </c>
       <c r="R9" t="n">
-        <v>6337916</v>
+        <v>6338060</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696394</v>
+        <v>123696505</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556497</v>
+        <v>556541</v>
       </c>
       <c r="R2" t="n">
-        <v>6338027</v>
+        <v>6338033</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696703</v>
+        <v>123696108</v>
       </c>
       <c r="B3" t="n">
         <v>100257</v>
@@ -813,14 +818,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556557</v>
+        <v>556601</v>
       </c>
       <c r="R3" t="n">
-        <v>6338080</v>
+        <v>6337896</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696272</v>
+        <v>123696925</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556538</v>
+        <v>556652</v>
       </c>
       <c r="R4" t="n">
-        <v>6337910</v>
+        <v>6338006</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696925</v>
+        <v>123696272</v>
       </c>
       <c r="B5" t="n">
         <v>100257</v>
@@ -1021,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556652</v>
+        <v>556538</v>
       </c>
       <c r="R5" t="n">
-        <v>6338006</v>
+        <v>6337910</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696505</v>
+        <v>123696703</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,46 +1100,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556541</v>
+        <v>556557</v>
       </c>
       <c r="R6" t="n">
-        <v>6338033</v>
+        <v>6338080</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696205</v>
+        <v>123696732</v>
       </c>
       <c r="B7" t="n">
         <v>100257</v>
@@ -1226,17 +1226,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556581</v>
+        <v>556592</v>
       </c>
       <c r="R7" t="n">
-        <v>6337916</v>
+        <v>6338060</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696108</v>
+        <v>123696394</v>
       </c>
       <c r="B8" t="n">
         <v>100257</v>
@@ -1328,17 +1328,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556601</v>
+        <v>556497</v>
       </c>
       <c r="R8" t="n">
-        <v>6337896</v>
+        <v>6338027</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696732</v>
+        <v>123696205</v>
       </c>
       <c r="B9" t="n">
         <v>100257</v>
@@ -1430,17 +1430,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556592</v>
+        <v>556581</v>
       </c>
       <c r="R9" t="n">
-        <v>6338060</v>
+        <v>6337916</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696505</v>
+        <v>123696108</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556541</v>
+        <v>556601</v>
       </c>
       <c r="R2" t="n">
-        <v>6338033</v>
+        <v>6337896</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696108</v>
+        <v>123696505</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556601</v>
+        <v>556541</v>
       </c>
       <c r="R3" t="n">
-        <v>6337896</v>
+        <v>6338033</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696505</v>
+        <v>123696703</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556541</v>
+        <v>556557</v>
       </c>
       <c r="R3" t="n">
-        <v>6338033</v>
+        <v>6338080</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696925</v>
+        <v>123696272</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -924,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556652</v>
+        <v>556538</v>
       </c>
       <c r="R4" t="n">
-        <v>6338006</v>
+        <v>6337910</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696272</v>
+        <v>123696394</v>
       </c>
       <c r="B5" t="n">
         <v>100257</v>
@@ -1022,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556538</v>
+        <v>556497</v>
       </c>
       <c r="R5" t="n">
-        <v>6337910</v>
+        <v>6338027</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696703</v>
+        <v>123696925</v>
       </c>
       <c r="B6" t="n">
         <v>100257</v>
@@ -1124,14 +1119,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556557</v>
+        <v>556652</v>
       </c>
       <c r="R6" t="n">
-        <v>6338080</v>
+        <v>6338006</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696732</v>
+        <v>123696505</v>
       </c>
       <c r="B7" t="n">
-        <v>100257</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,41 +1197,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556592</v>
+        <v>556541</v>
       </c>
       <c r="R7" t="n">
-        <v>6338060</v>
+        <v>6338033</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123696394</v>
+        <v>123696732</v>
       </c>
       <c r="B8" t="n">
         <v>100257</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556497</v>
+        <v>556592</v>
       </c>
       <c r="R8" t="n">
-        <v>6338027</v>
+        <v>6338060</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1494,108 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131537859</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5362</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörkan, Mörkan, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556454</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6338003</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123696272</v>
+        <v>133334414</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Nybygget, Lixhultsbrännan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556538</v>
+        <v>556583</v>
       </c>
       <c r="R2" t="n">
-        <v>6337910</v>
+        <v>6337855</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123696505</v>
+        <v>133334509</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +805,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Lixhultsbrännan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556541</v>
+        <v>556583</v>
       </c>
       <c r="R3" t="n">
-        <v>6338033</v>
+        <v>6337855</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,65 +901,72 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123696925</v>
+        <v>133334484</v>
       </c>
       <c r="B4" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>102987</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Nybygget, Lixhultsbrännan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556652</v>
+        <v>556583</v>
       </c>
       <c r="R4" t="n">
-        <v>6338006</v>
+        <v>6337855</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,27 +1020,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123696703</v>
+        <v>133334468</v>
       </c>
       <c r="B5" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +1043,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Lixhultsbrännan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556557</v>
+        <v>556583</v>
       </c>
       <c r="R5" t="n">
-        <v>6338080</v>
+        <v>6337855</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,12 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,27 +1139,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123696732</v>
+        <v>133334454</v>
       </c>
       <c r="B6" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,37 +1162,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Lixhultsbrännan, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556592</v>
+        <v>556583</v>
       </c>
       <c r="R6" t="n">
-        <v>6338060</v>
+        <v>6337855</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,12 +1228,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,65 +1258,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123696205</v>
+        <v>123696505</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nybygget, Nybygget, Sm</t>
+          <t>Mörkan, Mörkan, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556581</v>
+        <v>556541</v>
       </c>
       <c r="R7" t="n">
-        <v>6337916</v>
+        <v>6338033</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,12 +1375,7 @@
         <v>123696108</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,15 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123696394</v>
+        <v>123696205</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,17 +1500,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556497</v>
+        <v>556581</v>
       </c>
       <c r="R9" t="n">
-        <v>6338027</v>
+        <v>6337916</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,45 +1566,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131537859</v>
+        <v>123696272</v>
       </c>
       <c r="B10" t="n">
-        <v>5364</v>
+        <v>101326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101728</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörkan, Mörkan, Sm</t>
+          <t>Nybygget, Nybygget, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556454</v>
+        <v>556538</v>
       </c>
       <c r="R10" t="n">
-        <v>6338003</v>
+        <v>6337910</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1561,17 +1631,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Kläckhål</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1595,6 +1660,394 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123696394</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörkan, Mörkan, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556497</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6338027</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123696703</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörkan, Mörkan, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556557</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6338080</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123696732</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörkan, Mörkan, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>556592</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6338060</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123696925</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nybygget, Nybygget, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>556652</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6338006</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50746-2022 artfynd.xlsx
+++ b/artfynd/A 50746-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334414</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334509</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334484</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334468</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133334454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696505</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,6 +1501,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696108</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696205</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696272</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696394</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696703</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696732</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,8 +2113,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123696925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>